--- a/results/stock.xlsx
+++ b/results/stock.xlsx
@@ -465,19 +465,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1146999.278263127</v>
+        <v>1035773.726158066</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1146999.278263127</v>
+        <v>1035773.726158066</v>
       </c>
       <c r="E2" t="n">
-        <v>49458556.73467615</v>
+        <v>49434702.48623416</v>
       </c>
       <c r="F2" t="n">
-        <v>50605556.01293928</v>
+        <v>50470476.21239223</v>
       </c>
     </row>
     <row r="3">
@@ -485,19 +485,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1525165.880659537</v>
+        <v>1379763.273251337</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1525165.880659537</v>
+        <v>1379763.273251337</v>
       </c>
       <c r="E3" t="n">
-        <v>48485031.07559408</v>
+        <v>48550774.81323896</v>
       </c>
       <c r="F3" t="n">
-        <v>50010196.95625361</v>
+        <v>49930538.0864903</v>
       </c>
     </row>
     <row r="4">
@@ -505,19 +505,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1819700.853357395</v>
+        <v>1665334.884723084</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1819700.853357395</v>
+        <v>1665334.884723084</v>
       </c>
       <c r="E4" t="n">
-        <v>47982073.2953876</v>
+        <v>48169285.30528244</v>
       </c>
       <c r="F4" t="n">
-        <v>49801774.14874499</v>
+        <v>49834620.19000553</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +525,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1901179.583824972</v>
+        <v>1808889.237193129</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1901179.583824972</v>
+        <v>1808889.237193129</v>
       </c>
       <c r="E5" t="n">
-        <v>47931184.59034887</v>
+        <v>48271552.77805406</v>
       </c>
       <c r="F5" t="n">
-        <v>49832364.17417384</v>
+        <v>50080442.01524719</v>
       </c>
     </row>
     <row r="6">
@@ -545,19 +545,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1943462.411646292</v>
+        <v>1900676.441035645</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1943462.411646292</v>
+        <v>1900676.441035645</v>
       </c>
       <c r="E6" t="n">
-        <v>47894441.1993427</v>
+        <v>48313177.2243043</v>
       </c>
       <c r="F6" t="n">
-        <v>49837903.61098899</v>
+        <v>50213853.66533995</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +565,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1854427.755306635</v>
+        <v>1899520.966696591</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1854427.755306635</v>
+        <v>1899520.966696591</v>
       </c>
       <c r="E7" t="n">
-        <v>47785454.00699076</v>
+        <v>48247541.84173016</v>
       </c>
       <c r="F7" t="n">
-        <v>49639881.76229739</v>
+        <v>50147062.80842675</v>
       </c>
     </row>
     <row r="8">
@@ -585,19 +585,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1944765.397619904</v>
+        <v>1900602.570006344</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1944765.397619904</v>
+        <v>1900602.570006344</v>
       </c>
       <c r="E8" t="n">
-        <v>48081313.03371169</v>
+        <v>48452148.22593618</v>
       </c>
       <c r="F8" t="n">
-        <v>50026078.43133159</v>
+        <v>50352750.79594252</v>
       </c>
     </row>
     <row r="9">
@@ -605,19 +605,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1618751.847318216</v>
+        <v>1974623.668315135</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1618751.847318216</v>
+        <v>1974623.668315135</v>
       </c>
       <c r="E9" t="n">
-        <v>48395835.40924136</v>
+        <v>48942612.23075316</v>
       </c>
       <c r="F9" t="n">
-        <v>50014587.25655958</v>
+        <v>50917235.8990683</v>
       </c>
     </row>
     <row r="10">
@@ -625,19 +625,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1281538.70612917</v>
+        <v>1643832.116544785</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1281538.70612917</v>
+        <v>1643832.116544785</v>
       </c>
       <c r="E10" t="n">
-        <v>49234707.21529362</v>
+        <v>49431781.27751772</v>
       </c>
       <c r="F10" t="n">
-        <v>50516245.92142279</v>
+        <v>51075613.3940625</v>
       </c>
     </row>
     <row r="11">
@@ -645,19 +645,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1647603.39473688</v>
+        <v>2411047.524489974</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1647603.39473688</v>
+        <v>2411047.524489974</v>
       </c>
       <c r="E11" t="n">
-        <v>50711989.88827336</v>
+        <v>50560857.85502787</v>
       </c>
       <c r="F11" t="n">
-        <v>52359593.28301024</v>
+        <v>52971905.37951785</v>
       </c>
     </row>
   </sheetData>
